--- a/REPORTING MODULE/routes.xlsx
+++ b/REPORTING MODULE/routes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MY WORK FLOW\Emyris Onboard App\REPORTING MODULE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{886302EB-AC97-4C2D-B7B6-E4AC6A9A59BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E92D19-7D5D-419B-8CBD-DD66D1CE7E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="135">
   <si>
     <t>Sr no.</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Vadodara</t>
   </si>
   <si>
-    <t>Hyderabad Pst1</t>
-  </si>
-  <si>
     <t>Telangana</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>Cuttack</t>
   </si>
   <si>
-    <t>Bhuvneshwar</t>
-  </si>
-  <si>
     <t>Odisha</t>
   </si>
   <si>
@@ -150,9 +144,6 @@
     <t>Ranchi City</t>
   </si>
   <si>
-    <t>Ranchi</t>
-  </si>
-  <si>
     <t>Jharkhand</t>
   </si>
   <si>
@@ -174,9 +165,6 @@
     <t>Morbi</t>
   </si>
   <si>
-    <t>Rajkot Pst1</t>
-  </si>
-  <si>
     <t>Surendra Nagar</t>
   </si>
   <si>
@@ -204,9 +192,6 @@
     <t>Raipur City-1</t>
   </si>
   <si>
-    <t>Indore</t>
-  </si>
-  <si>
     <t>Madhya Pradesh</t>
   </si>
   <si>
@@ -276,18 +261,12 @@
     <t>Mehsana</t>
   </si>
   <si>
-    <t>Ahmedabad-2</t>
-  </si>
-  <si>
     <t>Patan</t>
   </si>
   <si>
     <t>Durg City</t>
   </si>
   <si>
-    <t>Durg</t>
-  </si>
-  <si>
     <t>Chhattisgarh</t>
   </si>
   <si>
@@ -303,9 +282,6 @@
     <t>Raipur City</t>
   </si>
   <si>
-    <t>Raipur-pst-1</t>
-  </si>
-  <si>
     <t>Kanpur City</t>
   </si>
   <si>
@@ -333,9 +309,6 @@
     <t>Korba</t>
   </si>
   <si>
-    <t>Bilaspur</t>
-  </si>
-  <si>
     <t>Raigarh</t>
   </si>
   <si>
@@ -354,9 +327,6 @@
     <t>Lormi</t>
   </si>
   <si>
-    <t>Bilaspur Pst 1</t>
-  </si>
-  <si>
     <t>Sipat</t>
   </si>
   <si>
@@ -366,9 +336,6 @@
     <t>Navasari City</t>
   </si>
   <si>
-    <t>Surat-2</t>
-  </si>
-  <si>
     <t>Chikhili Patch</t>
   </si>
   <si>
@@ -403,16 +370,82 @@
   </si>
   <si>
     <t>Approved By</t>
+  </si>
+  <si>
+    <t>HYDERABAD</t>
+  </si>
+  <si>
+    <t>VADODARA</t>
+  </si>
+  <si>
+    <t>VADODARA-PST-1</t>
+  </si>
+  <si>
+    <t>SURAT</t>
+  </si>
+  <si>
+    <t>BHUBANESWAR</t>
+  </si>
+  <si>
+    <t>LUCKNOW</t>
+  </si>
+  <si>
+    <t>RAJKOT</t>
+  </si>
+  <si>
+    <t>RANCHI</t>
+  </si>
+  <si>
+    <t>RAJKOT-PST-1</t>
+  </si>
+  <si>
+    <t>INDORE</t>
+  </si>
+  <si>
+    <t>AHMEDABAD</t>
+  </si>
+  <si>
+    <t>PUNE</t>
+  </si>
+  <si>
+    <t>NAGPUR</t>
+  </si>
+  <si>
+    <t>GHAZIABAD</t>
+  </si>
+  <si>
+    <t>DURG</t>
+  </si>
+  <si>
+    <t>RAIPUR</t>
+  </si>
+  <si>
+    <t>KANPUR</t>
+  </si>
+  <si>
+    <t>DELHI</t>
+  </si>
+  <si>
+    <t>BILASPUR</t>
+  </si>
+  <si>
+    <t>BILASPUR-PST-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -780,14 +813,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H146"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -813,7 +847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -827,16 +861,16 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2">
         <v>1041</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -847,19 +881,19 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
       </c>
       <c r="G3">
         <v>1323</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -870,19 +904,19 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -893,19 +927,19 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
       </c>
       <c r="G5">
         <v>946</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -916,19 +950,19 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -939,111 +973,111 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>1252</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1054,42 +1088,42 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" t="s">
         <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12">
         <v>1281</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1100,19 +1134,19 @@
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1123,65 +1157,65 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1192,19 +1226,19 @@
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" t="s">
         <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
       </c>
       <c r="G18">
         <v>1148</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1215,19 +1249,19 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" t="s">
         <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
       </c>
       <c r="G19">
         <v>1046</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1238,19 +1272,19 @@
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1261,42 +1295,42 @@
         <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21">
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1307,42 +1341,42 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23">
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" t="s">
         <v>30</v>
-      </c>
-      <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
       </c>
       <c r="G24">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1350,22 +1384,22 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1373,22 +1407,22 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1396,22 +1430,22 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G27">
         <v>1048</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1419,45 +1453,45 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G28">
         <v>1750</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G29">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1465,45 +1499,45 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G30">
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31">
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1511,22 +1545,22 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1537,19 +1571,19 @@
         <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1557,22 +1591,22 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="F34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1583,19 +1617,19 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35">
         <v>287</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1603,22 +1637,22 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D36" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1626,22 +1660,22 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1649,45 +1683,45 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" t="s">
         <v>40</v>
       </c>
-      <c r="D38" t="s">
-        <v>43</v>
-      </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="F38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="F39" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1695,22 +1729,22 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1721,19 +1755,19 @@
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1741,91 +1775,91 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F42" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G43">
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G44">
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
         <v>47</v>
       </c>
-      <c r="D45" t="s">
-        <v>51</v>
-      </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G45">
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1833,114 +1867,114 @@
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G47">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G48">
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G49">
         <v>174</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G50">
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1948,91 +1982,91 @@
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G51">
         <v>202</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G52">
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
       </c>
       <c r="D53" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G53">
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G54">
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2043,19 +2077,19 @@
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G55">
         <v>169</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2063,45 +2097,45 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E57" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="F57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G57">
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2112,19 +2146,19 @@
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2135,19 +2169,19 @@
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2155,68 +2189,68 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D60" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E60" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="F60" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D61" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E61" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G61">
         <v>106</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="F62" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G62">
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2227,19 +2261,19 @@
         <v>10</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2247,22 +2281,22 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2270,22 +2304,22 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="F65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2299,39 +2333,39 @@
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E67" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2342,65 +2376,65 @@
         <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G68">
         <v>211</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
       </c>
       <c r="D69" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G69">
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E70" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F70" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G70">
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2408,22 +2442,22 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D71" t="s">
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F71" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2431,22 +2465,22 @@
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D72" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E72" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F72" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2454,22 +2488,22 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D73" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E73" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F73" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2477,183 +2511,183 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D74" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E74" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="F74" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D75" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E75" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F75" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G75">
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E76" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F76" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G76">
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D77" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E77" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F77" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G77">
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D78" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E78" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F78" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G78">
         <v>51</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C79" t="s">
+        <v>66</v>
+      </c>
+      <c r="D79" t="s">
         <v>71</v>
       </c>
-      <c r="D79" t="s">
-        <v>76</v>
-      </c>
       <c r="E79" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F79" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G79">
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D80" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E80" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F80" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G80">
         <v>51</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D81" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E81" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F81" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G81">
         <v>63</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2664,19 +2698,19 @@
         <v>10</v>
       </c>
       <c r="D82" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2684,22 +2718,22 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D83" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E83" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F83" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2707,22 +2741,22 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D84" t="s">
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="F84" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2730,45 +2764,45 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E85" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="F85" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G86">
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2776,68 +2810,68 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D87" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E87" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F87" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G87">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D88" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E88" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="F88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G88">
         <v>65</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D89" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E89" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G89">
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2845,68 +2879,68 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E90" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D91" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E91" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F91" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G91">
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D92" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E92" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F92" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G92">
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2914,22 +2948,22 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D93" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E93" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="F93" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G93">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2937,22 +2971,22 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D94" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E94" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F94" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G94">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2960,22 +2994,22 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D95" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E95" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F95" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2983,22 +3017,22 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D96" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E96" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F96" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G96">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3006,22 +3040,22 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E97" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F97" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G97">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3032,19 +3066,19 @@
         <v>10</v>
       </c>
       <c r="D98" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E98" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G98">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3052,22 +3086,22 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D99" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E99" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="F99" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G99">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3078,19 +3112,19 @@
         <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E100" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="F100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3098,22 +3132,22 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D101" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E101" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F101" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G101">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3121,22 +3155,22 @@
         <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D102" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="F102" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G102">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3144,22 +3178,22 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E103" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="F103" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G103">
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3167,22 +3201,22 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D104" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E104" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="F104" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G104">
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3190,22 +3224,22 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D105" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E105" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F105" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G105">
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3213,22 +3247,22 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D106" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E106" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F106" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G106">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3236,22 +3270,22 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D107" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E107" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F107" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G107">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3259,137 +3293,137 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D108" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E108" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F108" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D109" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E109" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="F109" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G109">
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D110" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E110" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="F110" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G110">
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D111" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E111" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G111">
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D112" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E112" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="F112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G112">
         <v>68</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D113" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E113" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F113" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G113">
         <v>91</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3397,22 +3431,22 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D114" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E114" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F114" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G114">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3420,45 +3454,45 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D115" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E115" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F115" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G115">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D116" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E116" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F116" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G116">
         <v>116</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3466,68 +3500,68 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D117" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E117" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F117" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G117">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D118" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E118" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F118" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G118">
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D119" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E119" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F119" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G119">
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3535,22 +3569,22 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D120" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E120" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F120" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G120">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3561,19 +3595,19 @@
         <v>9</v>
       </c>
       <c r="D121" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E121" t="s">
+        <v>115</v>
+      </c>
+      <c r="F121" t="s">
         <v>11</v>
       </c>
-      <c r="F121" t="s">
-        <v>12</v>
-      </c>
       <c r="G121">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3581,183 +3615,183 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D122" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E122" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="F122" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G122">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C123" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E123" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F123" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G123">
         <v>65</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D124" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E124" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F124" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G124">
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D125" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E125" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G125">
         <v>40</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D126" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E126" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G126">
         <v>65.900000000000006</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D127" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E127" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G127">
         <v>74.2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C128" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D128" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E128" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G128">
         <v>93.9</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D129" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E129" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F129" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G129">
         <v>90.2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -3765,115 +3799,115 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D130" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E130" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F130" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G130">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C131" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D131" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E131" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F131" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G131">
         <v>106</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C132" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D132" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E132" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F132" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G132">
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C133" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D133" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E133" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="F133" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G133">
         <v>147</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H146" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 A4:D4 A2:D2 F2:H2 A3:D3 F3:H3 A11:D11 A5:D5 F5:H5 A17:D17 A12:D12 F12:H12 A120:D120 A18:D18 F18:H18 A19:D19 F19:H19 A134:H146 A121:D121 F121:H121 F4:H4 A6:D6 F6:H6 A7:D7 F7:H7 A8:D8 F8:H8 A9:D9 F9:H9 A10:D10 F10:H10 F11:H11 A13:D13 F13:H13 A14:D14 F14:H14 A15:D15 F15:H15 A16:D16 F16:H16 F17:H17 A20:D20 F20:H20 A21:D21 F21:H21 A22:D22 F22:H22 A23:D23 F23:H23 A24:D24 F24:H24 A25:D25 F25:H25 A26:D26 F26:H26 A27:D27 F27:H27 A28:D28 F28:H28 A29:D29 F29:H29 A30:D30 F30:H30 A31:D31 F31:H31 A32:D32 F32:H32 A33:D33 F33:H33 A34:D34 F34:H34 A35:D35 F35:H35 A36:D36 F36:H36 A37:D37 F37:H37 A38:D38 F38:H38 A39:D39 F39:H39 A40:D40 F40:H40 A41:D41 F41:H41 A42:D42 F42:H42 A43:D43 F43:H43 A44:D44 F44:H44 A45:D45 F45:H45 A46:D46 F46:H46 A47:D47 F47:H47 A48:D48 F48:H48 A49:D49 F49:H49 A50:D50 F50:H50 A51:D51 F51:H51 A52:D52 F52:H52 A53:D53 F53:H53 A54:D54 F54:H54 A55:D55 F55:H55 A56:D56 F56:H56 A57:D57 F57:H57 A58:D58 F58:H58 A59:D59 F59:H59 A60:D60 F60:H60 A61:D61 F61:H61 A62:D62 F62:H62 A63:D63 F63:H63 A64:D64 F64:H64 A65:D65 F65:H65 A66:D66 F66:H66 A67:D67 F67:H67 A68:D68 F68:H68 A69:D69 F69:H69 A70:D70 F70:H70 A71:D71 F71:H71 A72:D72 F72:H72 A73:D73 F73:H73 A74:D74 F74:H74 A75:D75 F75:H75 A76:D81 F76:H81 A82:D82 F82:H82 A83:D83 F83:H83 A84:D84 F84:H84 A85:D85 F85:H85 A86:D86 F86:H86 A87:D87 F87:H87 A88:D88 F88:H88 A89:D89 F89:H89 A90:D90 F90:H90 A91:D91 F91:H91 A92:D92 F92:H92 A93:D93 F93:H93 A94:D94 F94:H94 A95:D95 F95:H95 A96:D96 F96:H96 A97:D97 F97:H97 A98:D98 F98:H98 A99:D99 F99:H99 A100:D100 F100:H100 A101:D101 F101:H101 A102:D102 F102:H102 A103:D103 F103:H103 A104:D104 F104:H104 A105:D105 F105:H105 A106:D106 F106:H106 A107:D107 F107:H107 A108:D108 F108:H108 A109:D109 F109:H109 A110:D110 F110:H110 A111:D111 F111:H111 A112:D112 F112:H112 A113:D113 F113:H113 A114:D114 F114:H114 A115:D115 F115:H115 A116:D116 F116:H116 A117:D117 F117:H117 A118:D118 F118:H118 A119:D119 F119:H119 F120:H120 A122:D122 F122:H122 A123:D123 F123:H123 A124:D124 F124:H124 A125:D125 F125:H125 A126:D126 F126:H126 A127:D127 F127:H127 A128:D128 F128:H128 A129:D129 F129:H129 A130:D130 F130:H130 A131:D131 F131:H131 A132:D132 F132:H132 A133:D133 F133:H133" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>